--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/01009T-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/01009T-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FF25B33-DF9B-47CA-8472-4C0E1AD13F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B008B21-A12A-4621-8A0E-A11C07C6D263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{6F32410C-2F6F-48DC-BBF0-2981007E1CB4}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{F998D681-D727-4EC2-94A1-26358059E466}"/>
   </bookViews>
   <sheets>
     <sheet name="01009T-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1502,23 +1502,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5D7B80-5A1A-4792-838C-E26FAB2617BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB42610-4803-4F3E-9901-2C8F916E4A85}">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1546,7 +1546,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1576,7 +1576,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1672,7 +1672,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2336,7 +2336,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2020</v>
       </c>
@@ -2556,7 +2556,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2019</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39" t="s">
         <v>53</v>
       </c>
